--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:49:03+00:00</t>
+    <t>2024-01-29T09:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -986,7 +986,7 @@
     <t>The role a person plays representing an organization | Rôle (situation d'exercice) du professionnel de santé au sein de l'organisation. Correspond à la notion de Fonction dans le NOS.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-practitioner-role-exercice</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vspractitioner-role-exercice</t>
   </si>
   <si>
     <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
@@ -1007,7 +1007,7 @@
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-practitioner-specialty</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -1584,7 +1584,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="168.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.78125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.4921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:55:21+00:00</t>
+    <t>2024-01-29T12:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -986,7 +986,7 @@
     <t>The role a person plays representing an organization | Rôle (situation d'exercice) du professionnel de santé au sein de l'organisation. Correspond à la notion de Fonction dans le NOS.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vspractitioner-role-exercice</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice</t>
   </si>
   <si>
     <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
@@ -1584,7 +1584,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="168.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.4921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.15625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:33:53+00:00</t>
+    <t>2024-01-29T12:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-practitioner-role-exercice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:36:14+00:00</t>
+    <t>2024-01-29T12:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
